--- a/artfynd/A 46165-2024 artfynd.xlsx
+++ b/artfynd/A 46165-2024 artfynd.xlsx
@@ -2513,7 +2513,7 @@
         <v>88763534</v>
       </c>
       <c r="B19" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 46165-2024 artfynd.xlsx
+++ b/artfynd/A 46165-2024 artfynd.xlsx
@@ -2542,11 +2542,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 46165-2024 artfynd.xlsx
+++ b/artfynd/A 46165-2024 artfynd.xlsx
@@ -2513,7 +2513,7 @@
         <v>88763534</v>
       </c>
       <c r="B19" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
